--- a/remédios do Raul.xlsx
+++ b/remédios do Raul.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Raul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32519A2E-8FAB-4668-BD87-913D7F87FD5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550A59D5-07A5-45FE-A008-461BC9F8BBC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15760" windowHeight="5400" xr2:uid="{5263B8BD-719C-4D78-90D1-03E9B5E1C567}"/>
   </bookViews>
@@ -177,6 +177,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>466209</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>36576</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585C2953-1CCD-47BC-8B54-AA735BBCCE20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6642100" y="419100"/>
+          <a:ext cx="4123809" cy="12190476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>120838</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>197068</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7403191-7335-4748-A9D2-1AEF40F1426D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6153150" y="977900"/>
+          <a:ext cx="3657788" cy="4248368"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,5 +676,6 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>